--- a/informes_data/Tercera FEB/2025-26/playoffs/aggregate/AGGREGATE_OPOSITA MARÍN ENCE PEIXEGALEGO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/aggregate/AGGREGATE_OPOSITA MARÍN ENCE PEIXEGALEGO.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>239.6</v>
+        <v>469.6</v>
       </c>
       <c r="C2" t="n">
-        <v>237.38</v>
+        <v>467.8200000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>98.15485719100177</v>
+        <v>98.54217434055832</v>
       </c>
       <c r="E2" t="n">
-        <v>97.73359170949533</v>
+        <v>100.465991193194</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4569377990430622</v>
+        <v>0.4707317073170731</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1622002820874471</v>
+        <v>0.1511242167342425</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3410852713178295</v>
+        <v>0.28515625</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2009569377990431</v>
+        <v>0.1829268292682927</v>
       </c>
       <c r="J2" t="n">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="K2" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="L2" t="n">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="M2" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="N2" t="n">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="O2" t="n">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1913875598086124</v>
+        <v>0.2585365853658537</v>
       </c>
       <c r="Q2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="R2" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1170731707317073</v>
       </c>
       <c r="T2" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="U2" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.08048780487804878</v>
       </c>
       <c r="W2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="X2" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.138755980861244</v>
+        <v>0.1585365853658537</v>
       </c>
       <c r="Z2" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="AA2" t="n">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.3827751196172249</v>
+        <v>0.3853658536585366</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.55</v>
+        <v>0.5849056603773585</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3939393939393939</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2068965517241379</v>
+        <v>0.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.2875</v>
+        <v>0.310126582278481</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.1</v>
+        <v>1.169811320754717</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.7981651376146789</v>
+        <v>0.8340807174887892</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.3793103448275862</v>
+        <v>0.4742268041237113</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.4318181818181818</v>
+        <v>0.4657534246575342</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.533333333333333</v>
+        <v>2.27027027027027</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.8043478260869565</v>
+        <v>1.207317073170732</v>
       </c>
       <c r="AO2" t="n">
-        <v>4.543478260869565</v>
+        <v>5</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.347826086956522</v>
+        <v>6.207317073170731</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>79.86666666666667</v>
+        <v>78.26666666666667</v>
       </c>
       <c r="C3" t="n">
-        <v>79.12666666666667</v>
+        <v>77.97000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>98.15485719100178</v>
+        <v>98.54217434055832</v>
       </c>
       <c r="E3" t="n">
-        <v>97.73359170949533</v>
+        <v>100.4659911931939</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4569377990430621</v>
+        <v>0.4707317073170733</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1622002820874471</v>
+        <v>0.1511242167342425</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3410852713178295</v>
+        <v>0.28515625</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2009569377990431</v>
+        <v>0.1829268292682927</v>
       </c>
       <c r="J3" t="n">
-        <v>7.333333333333333</v>
+        <v>7.666666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>6.333333333333333</v>
+        <v>5.666666666666667</v>
       </c>
       <c r="L3" t="n">
-        <v>12.66666666666667</v>
+        <v>14</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="N3" t="n">
-        <v>7.333333333333333</v>
+        <v>10.33333333333333</v>
       </c>
       <c r="O3" t="n">
-        <v>13.33333333333333</v>
+        <v>17.66666666666667</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1913875598086124</v>
+        <v>0.2585365853658537</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.333333333333333</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="R3" t="n">
-        <v>12.66666666666667</v>
+        <v>8</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.1170731707317073</v>
       </c>
       <c r="T3" t="n">
-        <v>2.666666666666667</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="U3" t="n">
-        <v>7.333333333333333</v>
+        <v>5.5</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1052631578947368</v>
+        <v>0.08048780487804878</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="X3" t="n">
-        <v>9.666666666666666</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.138755980861244</v>
+        <v>0.1585365853658537</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.666666666666667</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="AA3" t="n">
-        <v>26.66666666666667</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3827751196172249</v>
+        <v>0.3853658536585366</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.5499999999999999</v>
+        <v>0.5849056603773585</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.5789473684210527</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3636363636363636</v>
+        <v>0.3939393939393939</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.206896551724138</v>
+        <v>0.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.2875</v>
+        <v>0.310126582278481</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.1</v>
+        <v>1.169811320754717</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.798165137614679</v>
+        <v>0.8340807174887892</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.3793103448275862</v>
+        <v>0.4742268041237113</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.4318181818181818</v>
+        <v>0.4657534246575343</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.533333333333333</v>
+        <v>2.27027027027027</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.8043478260869565</v>
+        <v>1.207317073170732</v>
       </c>
       <c r="AO3" t="n">
-        <v>4.543478260869565</v>
+        <v>5</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.347826086956522</v>
+        <v>6.207317073170731</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>235.16</v>
+        <v>466.0400000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>237.38</v>
+        <v>467.8200000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>97.73359170949533</v>
+        <v>100.465991193194</v>
       </c>
       <c r="E4" t="n">
-        <v>98.15485719100177</v>
+        <v>98.54217434055832</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5026737967914439</v>
+        <v>0.4832904884318766</v>
       </c>
       <c r="G4" t="n">
-        <v>0.212329770098111</v>
+        <v>0.1769943799722648</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3247863247863248</v>
+        <v>0.3388429752066116</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2416452442159383</v>
       </c>
       <c r="J4" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="K4" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="L4" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="M4" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="N4" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="O4" t="n">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2299465240641711</v>
+        <v>0.2570694087403599</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R4" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="S4" t="n">
-        <v>0.160427807486631</v>
+        <v>0.1285347043701799</v>
       </c>
       <c r="T4" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="U4" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1336898395721925</v>
+        <v>0.1131105398457583</v>
       </c>
       <c r="W4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="X4" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1016042780748663</v>
+        <v>0.141388174807198</v>
       </c>
       <c r="Z4" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="AA4" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.374331550802139</v>
+        <v>0.3598971722365039</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.5581395348837209</v>
+        <v>0.55</v>
       </c>
       <c r="AD4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.3863636363636364</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.3090909090909091</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.3357142857142857</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.7727272727272727</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.9846153846153847</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.6951219512195121</v>
+      </c>
+      <c r="AL4" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE4" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.2631578947368421</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0.3857142857142857</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.116279069767442</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.078651685393258</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0.8043478260869565</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0.5789473684210527</v>
-      </c>
       <c r="AM4" t="n">
-        <v>1.68</v>
+        <v>1.673469387755102</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.845360824742268</v>
       </c>
       <c r="AO4" t="n">
-        <v>3.224137931034483</v>
+        <v>4.010309278350515</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.844827586206896</v>
+        <v>4.855670103092783</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.38666666666667</v>
+        <v>77.67333333333335</v>
       </c>
       <c r="C5" t="n">
-        <v>79.12666666666667</v>
+        <v>77.97000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>97.73359170949533</v>
+        <v>100.4659911931939</v>
       </c>
       <c r="E5" t="n">
-        <v>98.15485719100178</v>
+        <v>98.54217434055832</v>
       </c>
       <c r="F5" t="n">
-        <v>0.502673796791444</v>
+        <v>0.4832904884318766</v>
       </c>
       <c r="G5" t="n">
-        <v>0.212329770098111</v>
+        <v>0.1769943799722648</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3247863247863248</v>
+        <v>0.3388429752066116</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2352941176470588</v>
+        <v>0.2416452442159382</v>
       </c>
       <c r="J5" t="n">
-        <v>12.33333333333333</v>
+        <v>9.5</v>
       </c>
       <c r="K5" t="n">
+        <v>6.833333333333333</v>
+      </c>
+      <c r="L5" t="n">
+        <v>13.66666666666667</v>
+      </c>
+      <c r="M5" t="n">
         <v>7.333333333333333</v>
       </c>
-      <c r="L5" t="n">
-        <v>14</v>
-      </c>
-      <c r="M5" t="n">
-        <v>8.666666666666666</v>
-      </c>
       <c r="N5" t="n">
-        <v>8</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="O5" t="n">
-        <v>14.33333333333333</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2299465240641712</v>
+        <v>0.2570694087403599</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="S5" t="n">
-        <v>0.160427807486631</v>
+        <v>0.1285347043701799</v>
       </c>
       <c r="T5" t="n">
-        <v>2.333333333333333</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="U5" t="n">
-        <v>8.333333333333334</v>
+        <v>7.333333333333333</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1336898395721925</v>
+        <v>0.1131105398457583</v>
       </c>
       <c r="W5" t="n">
-        <v>1.666666666666667</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="X5" t="n">
-        <v>6.333333333333333</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.1016042780748663</v>
+        <v>0.1413881748071979</v>
       </c>
       <c r="Z5" t="n">
-        <v>9</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="AA5" t="n">
         <v>23.33333333333333</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.374331550802139</v>
+        <v>0.3598971722365038</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.5581395348837209</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="AD5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.3863636363636364</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.3090909090909091</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.3357142857142857</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.7727272727272728</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.9846153846153847</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.6951219512195123</v>
+      </c>
+      <c r="AL5" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE5" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0.2631578947368421</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0.3857142857142857</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.116279069767442</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.5599999999999999</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.078651685393259</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>0.8043478260869565</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0.5789473684210527</v>
-      </c>
       <c r="AM5" t="n">
-        <v>1.68</v>
+        <v>1.673469387755102</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.6206896551724138</v>
+        <v>0.8453608247422679</v>
       </c>
       <c r="AO5" t="n">
-        <v>3.224137931034483</v>
+        <v>4.010309278350515</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.844827586206896</v>
+        <v>4.855670103092784</v>
       </c>
     </row>
     <row r="7">
@@ -1429,82 +1429,82 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="n">
+        <v>16</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>11</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
+        <v>6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>17</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
         <v>3</v>
       </c>
-      <c r="C8" t="n">
-        <v>7</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>5</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
         <v>4</v>
       </c>
-      <c r="H8" t="n">
+      <c r="X8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
-        <v>8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>8</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" t="n">
-        <v>-3</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" t="n">
         <v>1</v>
@@ -1516,19 +1516,19 @@
         <v>0.333</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -1537,54 +1537,54 @@
         <v>1</v>
       </c>
       <c r="AL8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>46:00</t>
+          <t>99:16</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>17.52</v>
+        <v>31.84</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.278</v>
+        <v>0.324</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.28</v>
+        <v>0.366</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.4</v>
+        <v>0.503</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.285</v>
+        <v>0.314</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.222</v>
+        <v>0.294</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AW8" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.161</v>
+        <v>0.142</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.081</v>
+        <v>0.057</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.111</v>
+        <v>0.1</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.063</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="9">
@@ -1594,64 +1594,64 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>28</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
         <v>3</v>
       </c>
-      <c r="C9" t="n">
+      <c r="F9" t="n">
+        <v>8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>27</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>9</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>3</v>
+      </c>
+      <c r="R9" t="n">
         <v>12</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" t="n">
-        <v>17</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
         <v>9</v>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-9</v>
-      </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1663,13 +1663,13 @@
         <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1690,66 +1690,66 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK9" t="n">
         <v>6</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AL9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>89:55</t>
+        </is>
+      </c>
+      <c r="AO9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AX9" t="n">
         <v>0.167</v>
       </c>
-      <c r="AK9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>11</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>43:44</t>
-        </is>
-      </c>
-      <c r="AO9" t="n">
-        <v>20</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0.194</v>
-      </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.117</v>
+        <v>0.099</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="10">
@@ -1759,40 +1759,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
+        <v>53</v>
+      </c>
+      <c r="D10" t="n">
         <v>21</v>
       </c>
-      <c r="D10" t="n">
-        <v>8</v>
-      </c>
       <c r="E10" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="H10" t="n">
+        <v>11</v>
+      </c>
+      <c r="I10" t="n">
+        <v>19</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34</v>
+      </c>
+      <c r="K10" t="n">
+        <v>9</v>
+      </c>
+      <c r="L10" t="n">
         <v>5</v>
       </c>
-      <c r="I10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>13</v>
-      </c>
-      <c r="K10" t="n">
-        <v>6</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2</v>
-      </c>
       <c r="M10" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="N10" t="n">
         <v>1</v>
@@ -1801,49 +1801,49 @@
         <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="U10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="Z10" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.222</v>
+        <v>0.538</v>
       </c>
       <c r="AB10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.5</v>
+        <v>0.462</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -1858,7 +1858,7 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -1867,54 +1867,54 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>175:39</t>
+        </is>
+      </c>
+      <c r="AO10" t="n">
+        <v>86.36</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>2.615</v>
+      </c>
+      <c r="AV10" t="n">
         <v>5</v>
       </c>
-      <c r="AM10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>87:14</t>
-        </is>
-      </c>
-      <c r="AO10" t="n">
-        <v>42.64</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0.303</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>4</v>
-      </c>
       <c r="AW10" t="n">
-        <v>5.625</v>
+        <v>7.615</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.207</v>
+        <v>0.217</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.021</v>
+        <v>0.027</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.051</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.178</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="11">
@@ -1924,22 +1924,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
         <v>2</v>
@@ -1948,13 +1948,13 @@
         <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="L11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
         <v>2</v>
@@ -1966,40 +1966,40 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="U11" t="n">
         <v>2</v>
       </c>
       <c r="V11" t="n">
+        <v>4</v>
+      </c>
+      <c r="W11" t="n">
         <v>2</v>
       </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Z11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.4</v>
+        <v>0.545</v>
       </c>
       <c r="AB11" t="n">
         <v>2</v>
@@ -2023,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
@@ -2039,44 +2039,44 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>39:38</t>
+          <t>78:13</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>13.76</v>
+        <v>23.76</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.625</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.615</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.872</v>
+        <v>0.842</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.291</v>
+        <v>0.253</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>2</v>
+        <v>2.667</v>
       </c>
       <c r="AW11" t="n">
-        <v>2.75</v>
+        <v>3.667</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.147</v>
+        <v>0.134</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.285</v>
+        <v>0.254</v>
       </c>
       <c r="BA11" t="n">
         <v>0.039</v>
@@ -2089,162 +2089,162 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>17</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>17</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>11</v>
+      </c>
+      <c r="U12" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="n">
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
         <v>3</v>
       </c>
-      <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK12" t="n">
         <v>4</v>
       </c>
-      <c r="H12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1</v>
-      </c>
       <c r="AL12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AM12" t="n">
         <v>0.333</v>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>31:11</t>
+          <t>67:30</t>
         </is>
       </c>
       <c r="AO12" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.3</v>
+        <v>0.447</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.3</v>
+        <v>0.447</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.333</v>
+        <v>0.654</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.444</v>
+        <v>0.269</v>
       </c>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.25</v>
+        <v>1.429</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.25</v>
+        <v>2.714</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.5</v>
+        <v>4.143</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.122</v>
+        <v>0.17</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.099</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.012</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="13">
@@ -2254,82 +2254,82 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" t="n">
+        <v>29</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>17</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8</v>
+      </c>
+      <c r="I13" t="n">
+        <v>11</v>
+      </c>
+      <c r="J13" t="n">
         <v>3</v>
       </c>
-      <c r="C13" t="n">
-        <v>12</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="K13" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" t="n">
+        <v>7</v>
+      </c>
+      <c r="M13" t="n">
         <v>3</v>
       </c>
-      <c r="E13" t="n">
-        <v>7</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>6</v>
-      </c>
-      <c r="I13" t="n">
-        <v>6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" t="n">
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q13" t="n">
         <v>5</v>
       </c>
-      <c r="L13" t="n">
-        <v>5</v>
-      </c>
-      <c r="M13" t="n">
+      <c r="R13" t="n">
+        <v>20</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>8</v>
+      </c>
+      <c r="U13" t="n">
+        <v>8</v>
+      </c>
+      <c r="V13" t="n">
+        <v>4</v>
+      </c>
+      <c r="W13" t="n">
+        <v>4</v>
+      </c>
+      <c r="X13" t="n">
         <v>2</v>
       </c>
-      <c r="N13" t="n">
-        <v>1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>10</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>4</v>
-      </c>
-      <c r="U13" t="n">
-        <v>6</v>
-      </c>
-      <c r="V13" t="n">
-        <v>2</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
       <c r="Y13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.5</v>
+        <v>0.571</v>
       </c>
       <c r="AB13" t="n">
         <v>1</v>
@@ -2359,57 +2359,57 @@
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>43:30</t>
+          <t>97:27</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>16.64</v>
+        <v>35.84</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.3</v>
+        <v>0.457</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.475</v>
+        <v>0.521</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.721</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.24</v>
+        <v>0.223</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.6</v>
+        <v>0.348</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.5</v>
+        <v>2.875</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.162</v>
+        <v>0.163</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.107</v>
+        <v>0.067</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.118</v>
+        <v>0.102</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="14">
@@ -2419,61 +2419,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E14" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
+        <v>13</v>
+      </c>
+      <c r="H14" t="n">
+        <v>23</v>
+      </c>
+      <c r="I14" t="n">
+        <v>33</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" t="n">
+        <v>37</v>
+      </c>
+      <c r="L14" t="n">
+        <v>14</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>4</v>
+      </c>
+      <c r="P14" t="n">
         <v>8</v>
       </c>
-      <c r="H14" t="n">
-        <v>10</v>
-      </c>
-      <c r="I14" t="n">
-        <v>18</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="Q14" t="n">
         <v>4</v>
       </c>
-      <c r="K14" t="n">
-        <v>21</v>
-      </c>
-      <c r="L14" t="n">
-        <v>7</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2</v>
-      </c>
-      <c r="P14" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
       <c r="R14" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -2482,28 +2482,28 @@
         <v>10</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="Z14" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.667</v>
+        <v>0.588</v>
       </c>
       <c r="AB14" t="n">
         <v>3</v>
       </c>
       <c r="AC14" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
@@ -2524,57 +2524,57 @@
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.625</v>
+        <v>0.538</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>75:30</t>
+          <t>139:38</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>33.92</v>
+        <v>64.52</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.717</v>
+        <v>0.607</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.695</v>
+        <v>0.655</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.268</v>
+        <v>1.147</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.124</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.435</v>
+        <v>0.548</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.333</v>
+        <v>0.875</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.667</v>
+        <v>5.25</v>
       </c>
       <c r="AW14" t="n">
-        <v>9</v>
+        <v>6.125</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.19</v>
+        <v>0.204</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.094</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.285</v>
+        <v>0.263</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="15">
@@ -2584,162 +2584,162 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>68</v>
+      </c>
+      <c r="D15" t="n">
+        <v>20</v>
+      </c>
+      <c r="E15" t="n">
+        <v>36</v>
+      </c>
+      <c r="F15" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>32</v>
+      </c>
+      <c r="H15" t="n">
+        <v>7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>9</v>
+      </c>
+      <c r="J15" t="n">
+        <v>10</v>
+      </c>
+      <c r="K15" t="n">
+        <v>26</v>
+      </c>
+      <c r="L15" t="n">
+        <v>7</v>
+      </c>
+      <c r="M15" t="n">
+        <v>10</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>14</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>55</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>10</v>
+      </c>
+      <c r="X15" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>10</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.778</v>
+      </c>
+      <c r="AE15" t="n">
         <v>3</v>
       </c>
-      <c r="C15" t="n">
-        <v>31</v>
-      </c>
-      <c r="D15" t="n">
-        <v>11</v>
-      </c>
-      <c r="E15" t="n">
-        <v>15</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1</v>
-      </c>
-      <c r="G15" t="n">
-        <v>11</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="AF15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK15" t="n">
         <v>6</v>
       </c>
-      <c r="I15" t="n">
-        <v>7</v>
-      </c>
-      <c r="J15" t="n">
-        <v>6</v>
-      </c>
-      <c r="K15" t="n">
-        <v>12</v>
-      </c>
-      <c r="L15" t="n">
-        <v>6</v>
-      </c>
-      <c r="M15" t="n">
-        <v>8</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>37</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2</v>
-      </c>
-      <c r="V15" t="n">
-        <v>3</v>
-      </c>
-      <c r="W15" t="n">
-        <v>6</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>5</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0.857</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
       <c r="AL15" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>88:30</t>
+          <t>180:45</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>34.08</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.481</v>
+        <v>0.449</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.533</v>
+        <v>0.472</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.147</v>
+        <v>0.122</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.231</v>
+        <v>0.103</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.163</v>
+        <v>0.201</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.063</v>
+        <v>0.036</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.139</v>
+        <v>0.143</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="16">
@@ -2749,22 +2749,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="H16" t="n">
         <v>2</v>
@@ -2773,49 +2773,49 @@
         <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>6</v>
+      </c>
+      <c r="M16" t="n">
         <v>2</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>20</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>14</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>14</v>
+      </c>
+      <c r="X16" t="n">
         <v>5</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>10</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>10</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>5</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2</v>
       </c>
       <c r="Y16" t="n">
         <v>3</v>
@@ -2839,51 +2839,51 @@
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI16" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.429</v>
+        <v>0.364</v>
       </c>
       <c r="AK16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AL16" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.182</v>
+        <v>0.316</v>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>52:25</t>
+          <t>85:45</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>24.88</v>
+        <v>37.88</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.479</v>
+        <v>0.514</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.502</v>
+        <v>0.528</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.005</v>
+        <v>1.056</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.083</v>
+        <v>0.054</v>
       </c>
       <c r="AU16" t="n">
         <v>0</v>
@@ -2895,16 +2895,16 @@
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.201</v>
+        <v>0.195</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.089</v>
+        <v>0.066</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.039</v>
+        <v>0.046</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.014</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="17">
@@ -2914,127 +2914,127 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>03:56</t>
+        </is>
+      </c>
+      <c r="AO17" t="n">
         <v>2</v>
       </c>
-      <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
       <c r="AP17" t="n">
         <v>0</v>
       </c>
@@ -3060,7 +3060,7 @@
         <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="AY17" t="n">
         <v>0</v>
@@ -3244,40 +3244,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E19" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="F19" t="n">
+        <v>23</v>
+      </c>
+      <c r="G19" t="n">
+        <v>65</v>
+      </c>
+      <c r="H19" t="n">
+        <v>17</v>
+      </c>
+      <c r="I19" t="n">
+        <v>26</v>
+      </c>
+      <c r="J19" t="n">
         <v>12</v>
       </c>
-      <c r="G19" t="n">
-        <v>36</v>
-      </c>
-      <c r="H19" t="n">
+      <c r="K19" t="n">
+        <v>19</v>
+      </c>
+      <c r="L19" t="n">
+        <v>6</v>
+      </c>
+      <c r="M19" t="n">
         <v>9</v>
-      </c>
-      <c r="I19" t="n">
-        <v>14</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" t="n">
-        <v>6</v>
-      </c>
-      <c r="L19" t="n">
-        <v>5</v>
-      </c>
-      <c r="M19" t="n">
-        <v>6</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
@@ -3286,120 +3286,120 @@
         <v>2</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q19" t="n">
         <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="U19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V19" t="n">
+        <v>4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>39</v>
+      </c>
+      <c r="X19" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>181:56</t>
+        </is>
+      </c>
+      <c r="AO19" t="n">
+        <v>108.44</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="AU19" t="n">
         <v>2</v>
       </c>
-      <c r="W19" t="n">
-        <v>24</v>
-      </c>
-      <c r="X19" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>92:18</t>
-        </is>
-      </c>
-      <c r="AO19" t="n">
-        <v>65.16</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0.537</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>1.028</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0.6</v>
-      </c>
       <c r="AV19" t="n">
-        <v>10.8</v>
+        <v>15.167</v>
       </c>
       <c r="AW19" t="n">
-        <v>11.4</v>
+        <v>17.167</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.299</v>
+        <v>0.264</v>
       </c>
       <c r="AY19" t="n">
-        <v>0.05</v>
+        <v>0.031</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.067</v>
+        <v>0.104</v>
       </c>
       <c r="BA19" t="n">
-        <v>0.052</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="20">
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -3436,10 +3436,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3451,10 +3451,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -3574,159 +3574,159 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>233</v>
+        <v>461</v>
       </c>
       <c r="D21" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="E21" t="n">
-        <v>100</v>
+        <v>187</v>
       </c>
       <c r="F21" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="G21" t="n">
-        <v>109</v>
+        <v>223</v>
       </c>
       <c r="H21" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="I21" t="n">
+        <v>115</v>
+      </c>
+      <c r="J21" t="n">
+        <v>99</v>
+      </c>
+      <c r="K21" t="n">
+        <v>160</v>
+      </c>
+      <c r="L21" t="n">
+        <v>73</v>
+      </c>
+      <c r="M21" t="n">
+        <v>53</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6</v>
+      </c>
+      <c r="O21" t="n">
+        <v>14</v>
+      </c>
+      <c r="P21" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>40</v>
+      </c>
+      <c r="R21" t="n">
+        <v>139</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>318</v>
+      </c>
+      <c r="U21" t="n">
+        <v>46</v>
+      </c>
+      <c r="V21" t="n">
+        <v>34</v>
+      </c>
+      <c r="W21" t="n">
+        <v>84</v>
+      </c>
+      <c r="X21" t="n">
+        <v>37</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>106</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>25</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>33</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI21" t="n">
         <v>65</v>
       </c>
-      <c r="J21" t="n">
-        <v>37</v>
-      </c>
-      <c r="K21" t="n">
-        <v>79</v>
-      </c>
-      <c r="L21" t="n">
-        <v>44</v>
-      </c>
-      <c r="M21" t="n">
-        <v>32</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3</v>
-      </c>
-      <c r="O21" t="n">
-        <v>10</v>
-      </c>
-      <c r="P21" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>21</v>
-      </c>
-      <c r="R21" t="n">
-        <v>65</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>152</v>
-      </c>
-      <c r="U21" t="n">
-        <v>22</v>
-      </c>
-      <c r="V21" t="n">
-        <v>19</v>
-      </c>
-      <c r="W21" t="n">
-        <v>38</v>
-      </c>
-      <c r="X21" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>29</v>
-      </c>
       <c r="AJ21" t="n">
-        <v>0.207</v>
+        <v>0.2</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="AL21" t="n">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.288</v>
+        <v>0.31</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>600:00</t>
+          <t>1200:00</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>283.6</v>
+        <v>542.6</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.457</v>
+        <v>0.471</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.822</v>
+        <v>0.85</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.162</v>
+        <v>0.151</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.201</v>
+        <v>0.183</v>
       </c>
       <c r="AU21" t="n">
-        <v>0.804</v>
+        <v>1.207</v>
       </c>
       <c r="AV21" t="n">
-        <v>4.543</v>
+        <v>5</v>
       </c>
       <c r="AW21" t="n">
-        <v>5.348</v>
+        <v>6.207</v>
       </c>
       <c r="AX21" t="n">
         <v>0.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.068</v>
+        <v>0.057</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.135</v>
+        <v>0.132</v>
       </c>
       <c r="BA21" t="n">
         <v>0</v>
@@ -3739,159 +3739,159 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>232</v>
+        <v>470</v>
       </c>
       <c r="D22" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="E22" t="n">
-        <v>98</v>
+        <v>194</v>
       </c>
       <c r="F22" t="n">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="G22" t="n">
-        <v>89</v>
+        <v>195</v>
       </c>
       <c r="H22" t="n">
+        <v>94</v>
+      </c>
+      <c r="I22" t="n">
+        <v>141</v>
+      </c>
+      <c r="J22" t="n">
+        <v>82</v>
+      </c>
+      <c r="K22" t="n">
+        <v>183</v>
+      </c>
+      <c r="L22" t="n">
+        <v>82</v>
+      </c>
+      <c r="M22" t="n">
+        <v>42</v>
+      </c>
+      <c r="N22" t="n">
+        <v>14</v>
+      </c>
+      <c r="O22" t="n">
+        <v>6</v>
+      </c>
+      <c r="P22" t="n">
+        <v>97</v>
+      </c>
+      <c r="Q22" t="n">
         <v>44</v>
       </c>
-      <c r="I22" t="n">
-        <v>64</v>
-      </c>
-      <c r="J22" t="n">
-        <v>36</v>
-      </c>
-      <c r="K22" t="n">
-        <v>85</v>
-      </c>
-      <c r="L22" t="n">
-        <v>38</v>
-      </c>
-      <c r="M22" t="n">
-        <v>25</v>
-      </c>
-      <c r="N22" t="n">
-        <v>10</v>
-      </c>
-      <c r="O22" t="n">
-        <v>3</v>
-      </c>
-      <c r="P22" t="n">
-        <v>58</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>26</v>
-      </c>
       <c r="R22" t="n">
-        <v>69</v>
+        <v>128</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>159</v>
+        <v>346</v>
       </c>
       <c r="U22" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="V22" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="W22" t="n">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="X22" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="Y22" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="Z22" t="n">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AC22" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AD22" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AE22" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="AF22" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="AG22" t="n">
-        <v>0.28</v>
+        <v>0.386</v>
       </c>
       <c r="AH22" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.263</v>
+        <v>0.309</v>
       </c>
       <c r="AK22" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="AL22" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.386</v>
+        <v>0.336</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>600:01</t>
+          <t>1200:01</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>273.16</v>
+        <v>548.04</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.503</v>
+        <v>0.483</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.539</v>
+        <v>0.521</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.849</v>
+        <v>0.858</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.212</v>
+        <v>0.177</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.235</v>
+        <v>0.242</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.621</v>
+        <v>0.845</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.224</v>
+        <v>4.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>3.845</v>
+        <v>4.856</v>
       </c>
       <c r="AX22" t="n">
         <v>0.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.065</v>
+        <v>0.068</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.132</v>
+        <v>0.143</v>
       </c>
       <c r="BA22" t="n">
         <v>0</v>
@@ -3963,28 +3963,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>2.333</v>
+        <v>2.667</v>
       </c>
       <c r="D24" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="E24" t="n">
-        <v>1.667</v>
+        <v>1.333</v>
       </c>
       <c r="F24" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="G24" t="n">
-        <v>1.333</v>
+        <v>1.5</v>
       </c>
       <c r="H24" t="n">
-        <v>0.667</v>
+        <v>0.833</v>
       </c>
       <c r="I24" t="n">
-        <v>2.667</v>
+        <v>1.833</v>
       </c>
       <c r="J24" t="n">
         <v>1.667</v>
@@ -3993,10 +3993,10 @@
         <v>1.667</v>
       </c>
       <c r="L24" t="n">
-        <v>1.333</v>
+        <v>1</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -4008,117 +4008,117 @@
         <v>1.667</v>
       </c>
       <c r="Q24" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y24" t="n">
         <v>0.333</v>
       </c>
-      <c r="R24" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>-3</v>
-      </c>
-      <c r="U24" t="n">
+      <c r="Z24" t="n">
         <v>0.333</v>
       </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="AC24" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AD24" t="n">
         <v>0.333</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AF24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
         <v>0.667</v>
       </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0.333</v>
-      </c>
       <c r="AJ24" t="n">
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="AL24" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.333</v>
+        <v>0.2</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>5.84</v>
+        <v>5.307</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.278</v>
+        <v>0.324</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.28</v>
+        <v>0.366</v>
       </c>
       <c r="AR24" t="n">
-        <v>0.4</v>
+        <v>0.503</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.285</v>
+        <v>0.314</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.222</v>
+        <v>0.294</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.161</v>
+        <v>0.142</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.081</v>
+        <v>0.057</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.111</v>
+        <v>0.1</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.063</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="25">
@@ -4128,22 +4128,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>4.667</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="E25" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="F25" t="n">
         <v>1.333</v>
       </c>
       <c r="G25" t="n">
-        <v>5.667</v>
+        <v>4.5</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -4152,16 +4152,16 @@
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K25" t="n">
-        <v>1.667</v>
+        <v>1.5</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>0.833</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
@@ -4173,43 +4173,43 @@
         <v>0.667</v>
       </c>
       <c r="Q25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R25" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>9</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="Y25" t="n">
         <v>0.333</v>
       </c>
-      <c r="R25" t="n">
-        <v>3</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="n">
-        <v>-9</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1</v>
-      </c>
-      <c r="X25" t="n">
+      <c r="Z25" t="n">
         <v>0.333</v>
       </c>
-      <c r="Y25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -4227,63 +4227,63 @@
         <v>0.333</v>
       </c>
       <c r="AI25" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="AJ25" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AO25" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="AX25" t="n">
         <v>0.167</v>
       </c>
-      <c r="AK25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AO25" t="n">
-        <v>6.667</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0.194</v>
-      </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>0.052</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.117</v>
+        <v>0.099</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="26">
@@ -4293,97 +4293,97 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>8.833</v>
       </c>
       <c r="D26" t="n">
-        <v>2.667</v>
+        <v>3.5</v>
       </c>
       <c r="E26" t="n">
-        <v>8</v>
+        <v>7.333</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>2.667</v>
+        <v>3.5</v>
       </c>
       <c r="H26" t="n">
-        <v>1.667</v>
+        <v>1.833</v>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>3.167</v>
       </c>
       <c r="J26" t="n">
-        <v>4.333</v>
+        <v>5.667</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L26" t="n">
-        <v>0.667</v>
+        <v>0.833</v>
       </c>
       <c r="M26" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="N26" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.667</v>
+        <v>2.167</v>
       </c>
       <c r="Q26" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="R26" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>32</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.667</v>
       </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>8</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.333</v>
-      </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y26" t="n">
-        <v>0.667</v>
+        <v>2.333</v>
       </c>
       <c r="Z26" t="n">
-        <v>3</v>
+        <v>4.333</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.222</v>
+        <v>0.538</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.667</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.333</v>
+        <v>2.167</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.5</v>
+        <v>0.462</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.667</v>
+        <v>0.833</v>
       </c>
       <c r="AG26" t="n">
         <v>0.2</v>
@@ -4392,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>1</v>
+        <v>1.167</v>
       </c>
       <c r="AJ26" t="n">
         <v>0</v>
@@ -4401,54 +4401,54 @@
         <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.667</v>
+        <v>2.333</v>
       </c>
       <c r="AM26" t="n">
         <v>0</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>29:04</t>
+          <t>29:16</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>14.213</v>
+        <v>14.393</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.25</v>
+        <v>0.323</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.303</v>
+        <v>0.361</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.492</v>
+        <v>0.614</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.188</v>
+        <v>0.151</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.156</v>
+        <v>0.169</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.625</v>
+        <v>2.615</v>
       </c>
       <c r="AV26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW26" t="n">
-        <v>5.625</v>
+        <v>7.615</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.207</v>
+        <v>0.217</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.021</v>
+        <v>0.027</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.051</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.178</v>
+        <v>0.241</v>
       </c>
     </row>
     <row r="27">
@@ -4458,40 +4458,40 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>3.333</v>
       </c>
       <c r="D27" t="n">
-        <v>1.667</v>
+        <v>1.5</v>
       </c>
       <c r="E27" t="n">
-        <v>2.667</v>
+        <v>2.333</v>
       </c>
       <c r="F27" t="n">
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="H27" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="I27" t="n">
         <v>0.667</v>
       </c>
-      <c r="I27" t="n">
-        <v>1.333</v>
-      </c>
       <c r="J27" t="n">
         <v>1</v>
       </c>
       <c r="K27" t="n">
-        <v>3.667</v>
+        <v>3.333</v>
       </c>
       <c r="L27" t="n">
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
@@ -4500,65 +4500,65 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.333</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="U27" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="V27" t="n">
         <v>0.667</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.667</v>
+        <v>1.833</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.4</v>
+        <v>0.545</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.667</v>
+        <v>0.333</v>
       </c>
       <c r="AD27" t="n">
         <v>1</v>
       </c>
       <c r="AE27" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
         <v>0.333</v>
       </c>
-      <c r="AF27" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ27" t="n">
         <v>0</v>
       </c>
@@ -4573,44 +4573,44 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>4.587</v>
+        <v>3.96</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.625</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.615</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.872</v>
+        <v>0.842</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.291</v>
+        <v>0.253</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="AU27" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AV27" t="n">
-        <v>2</v>
+        <v>2.667</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.75</v>
+        <v>3.667</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.147</v>
+        <v>0.134</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.285</v>
+        <v>0.254</v>
       </c>
       <c r="BA27" t="n">
         <v>0.039</v>
@@ -4623,22 +4623,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2.833</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="E28" t="n">
         <v>0.333</v>
       </c>
       <c r="F28" t="n">
-        <v>0.333</v>
+        <v>0.833</v>
       </c>
       <c r="G28" t="n">
-        <v>1.333</v>
+        <v>2.833</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -4647,7 +4647,7 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.333</v>
+        <v>1.667</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
@@ -4662,43 +4662,43 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28" t="n">
-        <v>1.333</v>
+        <v>1.167</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="R28" t="n">
-        <v>0.333</v>
+        <v>0.833</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4713,72 +4713,72 @@
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.333</v>
+        <v>0.833</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AK28" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="AL28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM28" t="n">
         <v>0.333</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>10:23</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>3</v>
+        <v>4.333</v>
       </c>
       <c r="AP28" t="n">
-        <v>0.3</v>
+        <v>0.447</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.3</v>
+        <v>0.447</v>
       </c>
       <c r="AR28" t="n">
-        <v>0.333</v>
+        <v>0.654</v>
       </c>
       <c r="AS28" t="n">
-        <v>0.444</v>
+        <v>0.269</v>
       </c>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>0.25</v>
+        <v>1.429</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.25</v>
+        <v>2.714</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.5</v>
+        <v>4.143</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.122</v>
+        <v>0.17</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.099</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="BA28" t="n">
-        <v>0.012</v>
+        <v>0.064</v>
       </c>
     </row>
     <row r="29">
@@ -4788,52 +4788,52 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>4.833</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="E29" t="n">
-        <v>2.333</v>
+        <v>2.833</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="G29" t="n">
         <v>1</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>1.333</v>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="J29" t="n">
-        <v>0.333</v>
+        <v>0.5</v>
       </c>
       <c r="K29" t="n">
         <v>1.667</v>
       </c>
       <c r="L29" t="n">
-        <v>1.667</v>
+        <v>1.167</v>
       </c>
       <c r="M29" t="n">
-        <v>0.667</v>
+        <v>0.5</v>
       </c>
       <c r="N29" t="n">
         <v>0.333</v>
       </c>
       <c r="O29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
         <v>1.333</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.667</v>
+        <v>0.833</v>
       </c>
       <c r="R29" t="n">
         <v>3.333</v>
@@ -4842,34 +4842,34 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1.333</v>
       </c>
       <c r="V29" t="n">
         <v>0.667</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>0.667</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.667</v>
+        <v>1.333</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.333</v>
+        <v>2.333</v>
       </c>
       <c r="AA29" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AC29" t="n">
         <v>0.5</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1</v>
       </c>
       <c r="AD29" t="n">
         <v>0.333</v>
@@ -4893,57 +4893,57 @@
         <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AL29" t="n">
         <v>1</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>5.547</v>
+        <v>5.973</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.3</v>
+        <v>0.457</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.475</v>
+        <v>0.521</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.721</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.24</v>
+        <v>0.223</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.6</v>
+        <v>0.348</v>
       </c>
       <c r="AU29" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.5</v>
+        <v>2.875</v>
       </c>
       <c r="AW29" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.162</v>
+        <v>0.163</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.107</v>
+        <v>0.067</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.118</v>
+        <v>0.102</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="30">
@@ -4953,97 +4953,97 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>14.333</v>
+        <v>12.333</v>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E30" t="n">
-        <v>5</v>
+        <v>4.833</v>
       </c>
       <c r="F30" t="n">
-        <v>1.667</v>
+        <v>1.167</v>
       </c>
       <c r="G30" t="n">
-        <v>2.667</v>
+        <v>2.167</v>
       </c>
       <c r="H30" t="n">
-        <v>3.333</v>
+        <v>3.833</v>
       </c>
       <c r="I30" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="J30" t="n">
-        <v>1.333</v>
+        <v>1.167</v>
       </c>
       <c r="K30" t="n">
-        <v>7</v>
+        <v>6.167</v>
       </c>
       <c r="L30" t="n">
         <v>2.333</v>
       </c>
       <c r="M30" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="O30" t="n">
+        <v>4</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="Q30" t="n">
         <v>0.667</v>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>81</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD30" t="n">
         <v>0.333</v>
       </c>
-      <c r="R30" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>48</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.333</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD30" t="n">
+      <c r="AE30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF30" t="n">
         <v>0.5</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1</v>
       </c>
       <c r="AG30" t="n">
         <v>0.667</v>
@@ -5058,57 +5058,57 @@
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.667</v>
+        <v>1.167</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.667</v>
+        <v>2.167</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.625</v>
+        <v>0.538</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>25:10</t>
+          <t>23:16</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>11.307</v>
+        <v>10.753</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.717</v>
+        <v>0.607</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.695</v>
+        <v>0.655</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.268</v>
+        <v>1.147</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.124</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.435</v>
+        <v>0.548</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.333</v>
+        <v>0.875</v>
       </c>
       <c r="AV30" t="n">
-        <v>7.667</v>
+        <v>5.25</v>
       </c>
       <c r="AW30" t="n">
-        <v>9</v>
+        <v>6.125</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.19</v>
+        <v>0.204</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.094</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.285</v>
+        <v>0.263</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="31">
@@ -5118,43 +5118,43 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>10.333</v>
+        <v>11.333</v>
       </c>
       <c r="D31" t="n">
-        <v>3.667</v>
+        <v>3.333</v>
       </c>
       <c r="E31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" t="n">
-        <v>0.333</v>
+        <v>1.167</v>
       </c>
       <c r="G31" t="n">
-        <v>3.667</v>
+        <v>5.333</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>1.167</v>
       </c>
       <c r="I31" t="n">
-        <v>2.333</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="K31" t="n">
-        <v>4</v>
+        <v>4.333</v>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>1.167</v>
       </c>
       <c r="M31" t="n">
-        <v>2.667</v>
+        <v>1.667</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -5163,117 +5163,117 @@
         <v>1.667</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.333</v>
+        <v>0.667</v>
       </c>
       <c r="R31" t="n">
-        <v>2</v>
+        <v>2.333</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="U31" t="n">
-        <v>0.667</v>
+        <v>0.833</v>
       </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="Y31" t="n">
         <v>1.667</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.667</v>
+        <v>3.167</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.625</v>
+        <v>0.526</v>
       </c>
       <c r="AB31" t="n">
-        <v>2</v>
+        <v>1.167</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.333</v>
+        <v>1.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.857</v>
+        <v>0.778</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.333</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>0.375</v>
       </c>
       <c r="AH31" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.333</v>
+        <v>1.667</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.333</v>
+        <v>3.667</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>0.273</v>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>29:30</t>
+          <t>30:07</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>11.36</v>
+        <v>13.66</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.481</v>
+        <v>0.449</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.533</v>
+        <v>0.472</v>
       </c>
       <c r="AR31" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.147</v>
+        <v>0.122</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.231</v>
+        <v>0.103</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AV31" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="AW31" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.163</v>
+        <v>0.201</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.063</v>
+        <v>0.036</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.139</v>
+        <v>0.143</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="32">
@@ -5283,43 +5283,43 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C32" t="n">
-        <v>8.333</v>
+        <v>6.667</v>
       </c>
       <c r="D32" t="n">
-        <v>1.333</v>
+        <v>0.667</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>1.167</v>
       </c>
       <c r="F32" t="n">
         <v>1.667</v>
       </c>
       <c r="G32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="J32" t="n">
         <v>0.667</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.333</v>
       </c>
       <c r="K32" t="n">
         <v>0.667</v>
       </c>
       <c r="L32" t="n">
-        <v>1.667</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>0.333</v>
       </c>
       <c r="N32" t="n">
-        <v>0.333</v>
+        <v>0.167</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -5337,34 +5337,34 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>1.667</v>
+        <v>2.333</v>
       </c>
       <c r="X32" t="n">
-        <v>0.667</v>
+        <v>0.833</v>
       </c>
       <c r="Y32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AA32" t="n">
         <v>1</v>
       </c>
       <c r="AB32" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="AC32" t="n">
         <v>0.333</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0.667</v>
       </c>
       <c r="AD32" t="n">
         <v>0.5</v>
@@ -5379,45 +5379,45 @@
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.333</v>
+        <v>1.833</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.429</v>
+        <v>0.364</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.667</v>
+        <v>1</v>
       </c>
       <c r="AL32" t="n">
-        <v>3.667</v>
+        <v>3.167</v>
       </c>
       <c r="AM32" t="n">
-        <v>0.182</v>
+        <v>0.316</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>17:28</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>8.292999999999999</v>
+        <v>6.313</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.479</v>
+        <v>0.514</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.502</v>
+        <v>0.528</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.005</v>
+        <v>1.056</v>
       </c>
       <c r="AS32" t="n">
         <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.083</v>
+        <v>0.054</v>
       </c>
       <c r="AU32" t="n">
         <v>0</v>
@@ -5429,16 +5429,16 @@
         <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.201</v>
+        <v>0.195</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.089</v>
+        <v>0.066</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.039</v>
+        <v>0.046</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.014</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="33">
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
@@ -5457,13 +5457,13 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -5496,13 +5496,13 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -5520,7 +5520,7 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
@@ -5547,7 +5547,7 @@
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AJ33" t="n">
         <v>0</v>
@@ -5563,11 +5563,11 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>00:47</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AP33" t="n">
         <v>0</v>
@@ -5594,7 +5594,7 @@
         <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>0.225</v>
       </c>
       <c r="AY33" t="n">
         <v>0</v>
@@ -5778,40 +5778,40 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C35" t="n">
-        <v>22.333</v>
+        <v>19.333</v>
       </c>
       <c r="D35" t="n">
-        <v>3.667</v>
+        <v>2.5</v>
       </c>
       <c r="E35" t="n">
-        <v>6</v>
+        <v>4.333</v>
       </c>
       <c r="F35" t="n">
-        <v>4</v>
+        <v>3.833</v>
       </c>
       <c r="G35" t="n">
-        <v>12</v>
+        <v>10.833</v>
       </c>
       <c r="H35" t="n">
-        <v>3</v>
+        <v>2.833</v>
       </c>
       <c r="I35" t="n">
-        <v>4.667</v>
+        <v>4.333</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>3.167</v>
       </c>
       <c r="L35" t="n">
-        <v>1.667</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -5820,120 +5820,120 @@
         <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>1.667</v>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="R35" t="n">
         <v>0.667</v>
       </c>
-      <c r="R35" t="n">
-        <v>1</v>
-      </c>
       <c r="S35" t="n">
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="U35" t="n">
-        <v>2.333</v>
+        <v>1.5</v>
       </c>
       <c r="V35" t="n">
         <v>0.667</v>
       </c>
       <c r="W35" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="X35" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.333</v>
+        <v>1</v>
       </c>
       <c r="Z35" t="n">
         <v>1.667</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="AB35" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.333</v>
+        <v>1</v>
       </c>
       <c r="AD35" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.333</v>
+        <v>0.833</v>
       </c>
       <c r="AF35" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AK35" t="n">
         <v>3</v>
       </c>
-      <c r="AG35" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0.143</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>3.667</v>
-      </c>
       <c r="AL35" t="n">
-        <v>9.667</v>
+        <v>8.333</v>
       </c>
       <c r="AM35" t="n">
-        <v>0.379</v>
+        <v>0.36</v>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>30:46</t>
+          <t>30:19</t>
         </is>
       </c>
       <c r="AO35" t="n">
-        <v>21.72</v>
+        <v>18.073</v>
       </c>
       <c r="AP35" t="n">
-        <v>0.537</v>
+        <v>0.544</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.028</v>
+        <v>1.07</v>
       </c>
       <c r="AS35" t="n">
-        <v>0.077</v>
+        <v>0.055</v>
       </c>
       <c r="AT35" t="n">
-        <v>0.167</v>
+        <v>0.187</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="AV35" t="n">
-        <v>10.8</v>
+        <v>15.167</v>
       </c>
       <c r="AW35" t="n">
-        <v>11.4</v>
+        <v>17.167</v>
       </c>
       <c r="AX35" t="n">
-        <v>0.299</v>
+        <v>0.264</v>
       </c>
       <c r="AY35" t="n">
-        <v>0.05</v>
+        <v>0.031</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.067</v>
+        <v>0.104</v>
       </c>
       <c r="BA35" t="n">
-        <v>0.052</v>
+        <v>0.097</v>
       </c>
     </row>
     <row r="36">
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -5970,10 +5970,10 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1</v>
+        <v>1.667</v>
       </c>
       <c r="L36" t="n">
-        <v>2.333</v>
+        <v>1.833</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5985,10 +5985,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -6108,159 +6108,159 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>77.667</v>
+        <v>76.833</v>
       </c>
       <c r="D37" t="n">
-        <v>17.333</v>
+        <v>16.667</v>
       </c>
       <c r="E37" t="n">
-        <v>33.333</v>
+        <v>31.167</v>
       </c>
       <c r="F37" t="n">
-        <v>9.667</v>
+        <v>10.333</v>
       </c>
       <c r="G37" t="n">
-        <v>36.333</v>
+        <v>37.167</v>
       </c>
       <c r="H37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I37" t="n">
+        <v>19.167</v>
+      </c>
+      <c r="J37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>26.667</v>
+      </c>
+      <c r="L37" t="n">
+        <v>12.167</v>
+      </c>
+      <c r="M37" t="n">
+        <v>8.833</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1</v>
+      </c>
+      <c r="O37" t="n">
         <v>14</v>
       </c>
-      <c r="I37" t="n">
-        <v>21.667</v>
-      </c>
-      <c r="J37" t="n">
-        <v>12.333</v>
-      </c>
-      <c r="K37" t="n">
+      <c r="P37" t="n">
+        <v>13.667</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="R37" t="n">
+        <v>23.167</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>318</v>
+      </c>
+      <c r="U37" t="n">
+        <v>7.667</v>
+      </c>
+      <c r="V37" t="n">
+        <v>5.667</v>
+      </c>
+      <c r="W37" t="n">
+        <v>14</v>
+      </c>
+      <c r="X37" t="n">
+        <v>6.167</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>10.333</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>17.667</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>4.167</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.521</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>2.167</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>10.833</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>8.167</v>
+      </c>
+      <c r="AL37" t="n">
         <v>26.333</v>
       </c>
-      <c r="L37" t="n">
-        <v>14.667</v>
-      </c>
-      <c r="M37" t="n">
-        <v>10.667</v>
-      </c>
-      <c r="N37" t="n">
-        <v>1</v>
-      </c>
-      <c r="O37" t="n">
-        <v>10</v>
-      </c>
-      <c r="P37" t="n">
-        <v>15.333</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>7</v>
-      </c>
-      <c r="R37" t="n">
-        <v>21.667</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>152</v>
-      </c>
-      <c r="U37" t="n">
-        <v>7.333</v>
-      </c>
-      <c r="V37" t="n">
-        <v>6.333</v>
-      </c>
-      <c r="W37" t="n">
-        <v>12.667</v>
-      </c>
-      <c r="X37" t="n">
+      <c r="AM37" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>200:00</t>
+        </is>
+      </c>
+      <c r="AO37" t="n">
+        <v>90.43300000000001</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="AV37" t="n">
         <v>5</v>
       </c>
-      <c r="Y37" t="n">
-        <v>7.333</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>13.333</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>7.333</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>12.667</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>2.667</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>7.333</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0.364</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>9.667</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0.207</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>7.667</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>26.667</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0.288</v>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>200:00</t>
-        </is>
-      </c>
-      <c r="AO37" t="n">
-        <v>94.533</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>0.822</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0.162</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>0.804</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>4.543</v>
-      </c>
       <c r="AW37" t="n">
-        <v>5.348</v>
+        <v>6.207</v>
       </c>
       <c r="AX37" t="n">
         <v>0.2</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.068</v>
+        <v>0.057</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.135</v>
+        <v>0.132</v>
       </c>
       <c r="BA37" t="n">
         <v>0</v>
@@ -6273,118 +6273,118 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>77.333</v>
+        <v>78.333</v>
       </c>
       <c r="D38" t="n">
         <v>15.333</v>
       </c>
       <c r="E38" t="n">
-        <v>32.667</v>
+        <v>32.333</v>
       </c>
       <c r="F38" t="n">
         <v>10.667</v>
       </c>
       <c r="G38" t="n">
-        <v>29.667</v>
+        <v>32.5</v>
       </c>
       <c r="H38" t="n">
-        <v>14.667</v>
+        <v>15.667</v>
       </c>
       <c r="I38" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>13.667</v>
+      </c>
+      <c r="K38" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="L38" t="n">
+        <v>13.667</v>
+      </c>
+      <c r="M38" t="n">
+        <v>7</v>
+      </c>
+      <c r="N38" t="n">
+        <v>2.333</v>
+      </c>
+      <c r="O38" t="n">
+        <v>6</v>
+      </c>
+      <c r="P38" t="n">
+        <v>16.167</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="R38" t="n">
         <v>21.333</v>
       </c>
-      <c r="J38" t="n">
-        <v>12</v>
-      </c>
-      <c r="K38" t="n">
-        <v>28.333</v>
-      </c>
-      <c r="L38" t="n">
-        <v>12.667</v>
-      </c>
-      <c r="M38" t="n">
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>346</v>
+      </c>
+      <c r="U38" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="V38" t="n">
+        <v>6.833</v>
+      </c>
+      <c r="W38" t="n">
+        <v>13.667</v>
+      </c>
+      <c r="X38" t="n">
+        <v>8.167</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>9.167</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>16.667</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>3.333</v>
+      </c>
+      <c r="AC38" t="n">
         <v>8.333</v>
       </c>
-      <c r="N38" t="n">
-        <v>3.333</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3</v>
-      </c>
-      <c r="P38" t="n">
-        <v>19.333</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>8.667</v>
-      </c>
-      <c r="R38" t="n">
-        <v>23</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>159</v>
-      </c>
-      <c r="U38" t="n">
-        <v>12.333</v>
-      </c>
-      <c r="V38" t="n">
+      <c r="AD38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>2.833</v>
+      </c>
+      <c r="AF38" t="n">
         <v>7.333</v>
       </c>
-      <c r="W38" t="n">
-        <v>14</v>
-      </c>
-      <c r="X38" t="n">
-        <v>8.333</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>8</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>14.333</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0.5580000000000001</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>2.333</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>8.333</v>
-      </c>
       <c r="AG38" t="n">
-        <v>0.28</v>
+        <v>0.386</v>
       </c>
       <c r="AH38" t="n">
-        <v>1.667</v>
+        <v>2.833</v>
       </c>
       <c r="AI38" t="n">
-        <v>6.333</v>
+        <v>9.167</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.263</v>
+        <v>0.309</v>
       </c>
       <c r="AK38" t="n">
-        <v>9</v>
+        <v>7.833</v>
       </c>
       <c r="AL38" t="n">
         <v>23.333</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.386</v>
+        <v>0.336</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
@@ -6392,40 +6392,40 @@
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>91.053</v>
+        <v>91.34</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.503</v>
+        <v>0.483</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.539</v>
+        <v>0.521</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.849</v>
+        <v>0.858</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.212</v>
+        <v>0.177</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.235</v>
+        <v>0.242</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.621</v>
+        <v>0.845</v>
       </c>
       <c r="AV38" t="n">
-        <v>3.224</v>
+        <v>4.01</v>
       </c>
       <c r="AW38" t="n">
-        <v>3.845</v>
+        <v>4.856</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.193</v>
+        <v>0.202</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.059</v>
+        <v>0.064</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.145</v>
+        <v>0.151</v>
       </c>
       <c r="BA38" t="n">
         <v>0</v>
